--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_arica_y_parinacota.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>30.77715557016268</v>
+      </c>
+      <c r="C2">
         <v>29.27416602409334</v>
-      </c>
-      <c r="C2">
-        <v>30.77715557016268</v>
       </c>
       <c r="D2">
         <v>3.415981173219336</v>
       </c>
       <c r="E2">
-        <v>18.29048690913399</v>
+        <v>19.22955416024957</v>
       </c>
       <c r="F2">
         <v>62.47995893061643</v>
       </c>
       <c r="G2">
-        <v>19.22955416024957</v>
+        <v>18.29048690913399</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>33.92330383480826</v>
+      </c>
+      <c r="C3">
         <v>56.04719764011799</v>
-      </c>
-      <c r="C3">
-        <v>33.92330383480826</v>
       </c>
       <c r="D3">
         <v>1.784210526315789</v>
       </c>
       <c r="E3">
-        <v>29.50310559006211</v>
+        <v>17.85714285714286</v>
       </c>
       <c r="F3">
         <v>52.63975155279503</v>
       </c>
       <c r="G3">
-        <v>17.85714285714286</v>
+        <v>29.50310559006211</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>34.50520833333333</v>
+      </c>
+      <c r="C4">
         <v>38.54166666666667</v>
-      </c>
-      <c r="C4">
-        <v>34.50520833333333</v>
       </c>
       <c r="D4">
         <v>2.594594594594595</v>
       </c>
       <c r="E4">
-        <v>22.27238525206923</v>
+        <v>19.93980436418359</v>
       </c>
       <c r="F4">
         <v>57.78781038374718</v>
       </c>
       <c r="G4">
-        <v>19.93980436418359</v>
+        <v>22.27238525206923</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>39.21568627450981</v>
+      </c>
+      <c r="C5">
         <v>42.64705882352941</v>
-      </c>
-      <c r="C5">
-        <v>39.21568627450981</v>
       </c>
       <c r="D5">
         <v>2.344827586206896</v>
       </c>
       <c r="E5">
-        <v>23.45013477088949</v>
+        <v>21.5633423180593</v>
       </c>
       <c r="F5">
         <v>54.98652291105121</v>
       </c>
       <c r="G5">
-        <v>21.5633423180593</v>
+        <v>23.45013477088949</v>
       </c>
     </row>
   </sheetData>
